--- a/General/samples/calculate_date/non_business_days.xlsx
+++ b/General/samples/calculate_date/non_business_days.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junichi\Git\Python\calculate_date\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\junichi\Git\knowledge-python\General\samples\calculate_date\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE18DEF0-6FAF-4384-A8C8-F2FCBD3ADE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1000A5C-643D-4BD0-979B-05780D43B84B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{FCE92C4D-BFDB-4162-8331-03FDA8839228}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{FCE92C4D-BFDB-4162-8331-03FDA8839228}"/>
   </bookViews>
   <sheets>
     <sheet name="非営業日マスタ" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -97,6 +97,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -433,615 +436,654 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A6982ED-A39F-4101-A6F1-437912CB11DD}">
-  <dimension ref="A1:A120"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="2">
-        <v>45658</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46023</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="2">
-        <v>45661</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46024</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="2">
-        <v>45662</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46025</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="2">
-        <v>45668</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46026</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
-        <v>45669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46032</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
-        <v>45670</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46033</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
-        <v>45675</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46034</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
-        <v>45676</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46039</v>
+      </c>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
-        <v>45682</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46040</v>
+      </c>
+      <c r="E10" s="3"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
-        <v>45683</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46046</v>
+      </c>
+      <c r="E11" s="3"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
-        <v>45689</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46047</v>
+      </c>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
-        <v>45690</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46053</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
-        <v>45696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46054</v>
+      </c>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
-        <v>45697</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46060</v>
+      </c>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
-        <v>45699</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46061</v>
+      </c>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
-        <v>45703</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46064</v>
+      </c>
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
-        <v>45704</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46067</v>
+      </c>
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
-        <v>45710</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46068</v>
+      </c>
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
-        <v>45711</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46074</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
-        <v>45712</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46075</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
-        <v>45717</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
-        <v>45718</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46081</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
-        <v>45724</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
-        <v>45725</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
-        <v>45731</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46089</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
-        <v>45732</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
-        <v>45736</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
-        <v>45738</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
-        <v>45739</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
-        <v>45745</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
-        <v>45746</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
-        <v>45752</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
-        <v>45753</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
-        <v>45759</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
-        <v>45760</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
-        <v>45766</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
-        <v>45767</v>
+        <v>46130</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
-        <v>45773</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
-        <v>45774</v>
+        <v>46137</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
-        <v>45776</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A42" s="2">
-        <v>45780</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
-        <v>45781</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A44" s="2">
-        <v>45782</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A45" s="2">
-        <v>45783</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A46" s="2">
-        <v>45787</v>
+        <v>46147</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
-        <v>45788</v>
+        <v>46148</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A48" s="2">
-        <v>45794</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A49" s="2">
-        <v>45795</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A50" s="2">
-        <v>45801</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A51" s="2">
-        <v>45802</v>
+        <v>46159</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
-        <v>45808</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
-        <v>45809</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A54" s="2">
-        <v>45815</v>
+        <v>46172</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A55" s="2">
-        <v>45816</v>
+        <v>46173</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
-        <v>45822</v>
+        <v>46179</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A57" s="2">
-        <v>45823</v>
+        <v>46180</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A58" s="2">
-        <v>45829</v>
+        <v>46186</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A59" s="2">
-        <v>45830</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A60" s="2">
-        <v>45836</v>
+        <v>46193</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A61" s="2">
-        <v>45837</v>
+        <v>46194</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A62" s="2">
-        <v>45843</v>
+        <v>46200</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A63" s="2">
-        <v>45844</v>
+        <v>46201</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A64" s="2">
-        <v>45850</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A65" s="2">
-        <v>45851</v>
+        <v>46208</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A66" s="2">
-        <v>45857</v>
+        <v>46214</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A67" s="2">
-        <v>45858</v>
+        <v>46215</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A68" s="2">
-        <v>45859</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
-        <v>45864</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
-        <v>45865</v>
+        <v>46223</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
-        <v>45871</v>
+        <v>46228</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A72" s="2">
-        <v>45872</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A73" s="2">
-        <v>45878</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A74" s="2">
-        <v>45879</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A75" s="2">
-        <v>45880</v>
+        <v>46242</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A76" s="2">
-        <v>45885</v>
+        <v>46243</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A77" s="2">
-        <v>45886</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A78" s="2">
-        <v>45892</v>
+        <v>46249</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A79" s="2">
-        <v>45893</v>
+        <v>46250</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A80" s="2">
-        <v>45899</v>
+        <v>46256</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
-        <v>45900</v>
+        <v>46257</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A82" s="2">
-        <v>45906</v>
+        <v>46263</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A83" s="2">
-        <v>45907</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A84" s="2">
-        <v>45913</v>
+        <v>46270</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A85" s="2">
-        <v>45914</v>
+        <v>46271</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A86" s="2">
-        <v>45915</v>
+        <v>46277</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A87" s="2">
-        <v>45920</v>
+        <v>46278</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A88" s="2">
-        <v>45921</v>
+        <v>46284</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A89" s="2">
-        <v>45923</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A90" s="2">
-        <v>45927</v>
+        <v>46286</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A91" s="2">
-        <v>45928</v>
+        <v>46287</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A92" s="2">
-        <v>45934</v>
+        <v>46288</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A93" s="2">
-        <v>45935</v>
+        <v>46291</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A94" s="2">
-        <v>45941</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A95" s="2">
-        <v>45942</v>
+        <v>46298</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A96" s="2">
-        <v>45943</v>
+        <v>46299</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
-        <v>45948</v>
+        <v>46305</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A98" s="2">
-        <v>45949</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A99" s="2">
-        <v>45955</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
-        <v>45956</v>
+        <v>46312</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A101" s="2">
-        <v>45962</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A102" s="2">
-        <v>45963</v>
+        <v>46319</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
-        <v>45964</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A104" s="2">
-        <v>45969</v>
+        <v>46326</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A105" s="2">
-        <v>45970</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A106" s="2">
-        <v>45976</v>
+        <v>46329</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A107" s="2">
-        <v>45977</v>
+        <v>46333</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A108" s="2">
-        <v>45983</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A109" s="2">
-        <v>45984</v>
+        <v>46340</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A110" s="2">
-        <v>45985</v>
+        <v>46341</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A111" s="2">
-        <v>45990</v>
+        <v>46347</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A112" s="2">
-        <v>45991</v>
+        <v>46348</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A113" s="2">
-        <v>45997</v>
+        <v>46349</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A114" s="2">
-        <v>45998</v>
+        <v>46354</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A115" s="2">
-        <v>46004</v>
+        <v>46355</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A116" s="2">
-        <v>46005</v>
+        <v>46361</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A117" s="2">
-        <v>46011</v>
+        <v>46362</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A118" s="2">
-        <v>46012</v>
+        <v>46368</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A119" s="2">
-        <v>46018</v>
+        <v>46369</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A120" s="2">
-        <v>46019</v>
-      </c>
+        <v>46375</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A121" s="2">
+        <v>46376</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A122" s="2">
+        <v>46382</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A123" s="2">
+        <v>46383</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A125" s="2"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A126" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A143">
-    <sortCondition ref="A2:A143"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A123">
+    <sortCondition ref="A2:A123"/>
   </sortState>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
